--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,16 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Desktop\Dmart_sales_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9871EFBD-4F02-4F00-81CB-CDFEEF733F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CD2D1F-4C31-4B8B-BA6B-DD62E7807F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{5605ABE3-596F-461D-BB5E-9FB002AB002D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="6" xr2:uid="{5605ABE3-596F-461D-BB5E-9FB002AB002D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet5" sheetId="5" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId5"/>
+    <sheet name="string functions" sheetId="6" r:id="rId3"/>
+    <sheet name="DATE FUNCTIONS" sheetId="7" r:id="rId4"/>
+    <sheet name="Sheet8" sheetId="8" r:id="rId5"/>
+    <sheet name="STATITICAL FUNCTION" sheetId="9" r:id="rId6"/>
+    <sheet name="CONDITIONAL FORMATTING" sheetId="10" r:id="rId7"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId8"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId9"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="SALES_2025">Sheet5!$B$2:$B$10</definedName>
@@ -43,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="185">
   <si>
     <t>A</t>
   </si>
@@ -214,13 +219,397 @@
   </si>
   <si>
     <t>SALES 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          mlcRosOft   ExceL       </t>
+  </si>
+  <si>
+    <t>Basic functions in excel :</t>
+  </si>
+  <si>
+    <t>len(text)</t>
+  </si>
+  <si>
+    <t>upper(text)</t>
+  </si>
+  <si>
+    <t>lower(text)</t>
+  </si>
+  <si>
+    <t>proper(text)</t>
+  </si>
+  <si>
+    <t>returns the length of a string including spaces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trim(text) (both leading and trailing space) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">removes extra spaces except for single spaces between words </t>
+  </si>
+  <si>
+    <t xml:space="preserve">converts text to uppercase </t>
+  </si>
+  <si>
+    <t xml:space="preserve">converts text to lowercase </t>
+  </si>
+  <si>
+    <t>capitalize the first letter of each word</t>
+  </si>
+  <si>
+    <t xml:space="preserve">example </t>
+  </si>
+  <si>
+    <t xml:space="preserve">trim- </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     mocLOhdy ExceLLL     </t>
+  </si>
+  <si>
+    <t>Upper</t>
+  </si>
+  <si>
+    <t>jhhDdcsdnsjcb</t>
+  </si>
+  <si>
+    <t>lower</t>
+  </si>
+  <si>
+    <t>DJHCGDUYSCH</t>
+  </si>
+  <si>
+    <t>PROPER</t>
+  </si>
+  <si>
+    <t>gayathri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXAMPLE </t>
+  </si>
+  <si>
+    <t>LEN</t>
+  </si>
+  <si>
+    <t>String extraction functions:</t>
+  </si>
+  <si>
+    <t>left()</t>
+  </si>
+  <si>
+    <t>right()</t>
+  </si>
+  <si>
+    <t>mid()</t>
+  </si>
+  <si>
+    <t>extract specified numbers of character from the start</t>
+  </si>
+  <si>
+    <t>extract specified numbers of character from the end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">extract a substring from the middle </t>
+  </si>
+  <si>
+    <t>find ()</t>
+  </si>
+  <si>
+    <t>find the position of a substing case-sentive</t>
+  </si>
+  <si>
+    <t>Hello WorldW</t>
+  </si>
+  <si>
+    <t>Search()</t>
+  </si>
+  <si>
+    <t>Replace</t>
+  </si>
+  <si>
+    <t>replace(old text,starting no of word,how many letter of word,"replacing word")</t>
+  </si>
+  <si>
+    <t>Substitute</t>
+  </si>
+  <si>
+    <t>hello gayathri</t>
+  </si>
+  <si>
+    <t>sub(select the word cell,"type old word","new word")</t>
+  </si>
+  <si>
+    <t>concate</t>
+  </si>
+  <si>
+    <t>hello</t>
+  </si>
+  <si>
+    <t>hi</t>
+  </si>
+  <si>
+    <t>to add two string (b30,c30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENERATE DATE AND TIME </t>
+  </si>
+  <si>
+    <t>TODAY()</t>
+  </si>
+  <si>
+    <t>NOW()</t>
+  </si>
+  <si>
+    <t>EXTRACT DATE COMPONENTS</t>
+  </si>
+  <si>
+    <t>YEAR()</t>
+  </si>
+  <si>
+    <t>MONTH()</t>
+  </si>
+  <si>
+    <t>DAY()</t>
+  </si>
+  <si>
+    <t>WEEKDAY()</t>
+  </si>
+  <si>
+    <t>WEEKNUM()</t>
+  </si>
+  <si>
+    <t>TEXT()</t>
+  </si>
+  <si>
+    <t>DATEIF</t>
+  </si>
+  <si>
+    <t>YEAR DIFF</t>
+  </si>
+  <si>
+    <t>MNT DIFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAYS </t>
+  </si>
+  <si>
+    <t>EDATE</t>
+  </si>
+  <si>
+    <t>FROM TODAY ADDING 3 MNTHS</t>
+  </si>
+  <si>
+    <t>SR. NO</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>John Smith</t>
+  </si>
+  <si>
+    <t>ID-2024-NY-Active</t>
+  </si>
+  <si>
+    <t>Sarah Jenkins</t>
+  </si>
+  <si>
+    <t>ID-2025-CA-Pending</t>
+  </si>
+  <si>
+    <t>Michael Chang</t>
+  </si>
+  <si>
+    <t>FIRST NAME</t>
+  </si>
+  <si>
+    <t>EMAIL</t>
+  </si>
+  <si>
+    <t>ID-2025-TX-Active</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Sarah</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>STATE</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>TX</t>
+  </si>
+  <si>
+    <t>CNTRL+E TO EXTRACT AUTOM</t>
+  </si>
+  <si>
+    <t>s.john@company.com</t>
+  </si>
+  <si>
+    <t>j.sarah@company.com</t>
+  </si>
+  <si>
+    <t>c.michael@company.com</t>
+  </si>
+  <si>
+    <t>FLASH FILL</t>
+  </si>
+  <si>
+    <t>CHENNAI</t>
+  </si>
+  <si>
+    <t>BANGLORE</t>
+  </si>
+  <si>
+    <t>PUNE</t>
+  </si>
+  <si>
+    <t>COIMBATORE</t>
+  </si>
+  <si>
+    <t>JAN</t>
+  </si>
+  <si>
+    <t>FEB</t>
+  </si>
+  <si>
+    <t>MAR</t>
+  </si>
+  <si>
+    <t>APR</t>
+  </si>
+  <si>
+    <t>MAY</t>
+  </si>
+  <si>
+    <t>JUN</t>
+  </si>
+  <si>
+    <t>JUL</t>
+  </si>
+  <si>
+    <t>AUG</t>
+  </si>
+  <si>
+    <t>SEP</t>
+  </si>
+  <si>
+    <t>OCT</t>
+  </si>
+  <si>
+    <t>NOV</t>
+  </si>
+  <si>
+    <t>DEC</t>
+  </si>
+  <si>
+    <t>chennai</t>
+  </si>
+  <si>
+    <t>banglore</t>
+  </si>
+  <si>
+    <t>pune</t>
+  </si>
+  <si>
+    <t>coimbatore</t>
+  </si>
+  <si>
+    <t>file-more-option-advance- general-custome list-add yours</t>
+  </si>
+  <si>
+    <t>To custome</t>
+  </si>
+  <si>
+    <t>MEAN</t>
+  </si>
+  <si>
+    <t>MEDIAN</t>
+  </si>
+  <si>
+    <t>FUNC</t>
+  </si>
+  <si>
+    <t>FORMULA</t>
+  </si>
+  <si>
+    <t>MODE</t>
+  </si>
+  <si>
+    <t>(n+1)/2</t>
+  </si>
+  <si>
+    <t>MULTI MODE</t>
+  </si>
+  <si>
+    <t>DEVIATION</t>
+  </si>
+  <si>
+    <t>SQ DEVIATION</t>
+  </si>
+  <si>
+    <t>VARIANCE</t>
+  </si>
+  <si>
+    <t>AVG OF SQ DEV</t>
+  </si>
+  <si>
+    <t>STANDARD DEVIATION</t>
+  </si>
+  <si>
+    <t>take sq r of variance</t>
+  </si>
+  <si>
+    <t>PRODUCT 1</t>
+  </si>
+  <si>
+    <t>PRODUCT 2</t>
+  </si>
+  <si>
+    <t>PRODUCT 4</t>
+  </si>
+  <si>
+    <t>PRODUCT 3</t>
+  </si>
+  <si>
+    <t>PRODUCT 5</t>
+  </si>
+  <si>
+    <t>PRODUCT 6</t>
+  </si>
+  <si>
+    <t>PRODUCT 7</t>
+  </si>
+  <si>
+    <t>highlight cell</t>
+  </si>
+  <si>
+    <t>top/bottom rule</t>
+  </si>
+  <si>
+    <t>data bar</t>
+  </si>
+  <si>
+    <t>color scale</t>
+  </si>
+  <si>
+    <t>icon set</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -244,8 +633,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -255,6 +650,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -287,7 +688,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -306,12 +707,762 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="81">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1109,6 +2260,68 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C69E469F-FBB3-4F0E-A852-A8C4944018FB}">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1000</v>
+      </c>
+      <c r="B2">
+        <v>12</v>
+      </c>
+      <c r="F2">
+        <v>0.1</v>
+      </c>
+      <c r="G2">
+        <f>D2*F2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D3">
+        <f>A2*B2</f>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C5">
+        <f>A2+100</f>
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <f>A2*0.1</f>
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{209F4F9D-9D48-4862-8465-8D9D00B845AF}">
   <dimension ref="A1:I21"/>
@@ -1617,6 +2830,1321 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6C080A5-3897-4407-A839-7B8472F79A42}">
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" t="str">
+        <f>TRIM(F1)</f>
+        <v>mocLOhdy ExceLLL</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J6">
+        <f>LEN(A1)</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I8" t="s">
+        <v>70</v>
+      </c>
+      <c r="J8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K8" t="str">
+        <f>TRIM(J8)</f>
+        <v>mocLOhdy ExceLLL</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I10" t="s">
+        <v>72</v>
+      </c>
+      <c r="J10" t="s">
+        <v>73</v>
+      </c>
+      <c r="K10" t="str">
+        <f>UPPER(J10)</f>
+        <v>JHHDDCSDNSJCB</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J12" t="s">
+        <v>75</v>
+      </c>
+      <c r="K12" t="str">
+        <f>LOWER(J12)</f>
+        <v>djhcgduysch</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I14" t="s">
+        <v>76</v>
+      </c>
+      <c r="J14" t="s">
+        <v>77</v>
+      </c>
+      <c r="K14" t="str">
+        <f>PROPER(J14)</f>
+        <v>Gayathri</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" t="str">
+        <f>LEFT(C17,5)</f>
+        <v>Hello</v>
+      </c>
+      <c r="E18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" t="str">
+        <f>RIGHT(C17,5)</f>
+        <v>orldW</v>
+      </c>
+      <c r="E19" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" t="str">
+        <f>MID(C17,6,5)</f>
+        <v xml:space="preserve"> Worl</v>
+      </c>
+      <c r="E20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22">
+        <f>FIND("W",C17)</f>
+        <v>7</v>
+      </c>
+      <c r="E22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23">
+        <f>SEARCH("w",C17)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C25">
+        <f>FIND("W",C17,8)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" t="str">
+        <f>REPLACE(C17,7,6,"Excel")</f>
+        <v>Hello Excel</v>
+      </c>
+      <c r="E26" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B27" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" t="str">
+        <f>SUBSTITUTE(B27,"hello","hi")</f>
+        <v>hi gayathri</v>
+      </c>
+      <c r="E28" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C31" t="str">
+        <f>_xlfn.CONCAT(B30,C30)</f>
+        <v>hellohi</v>
+      </c>
+      <c r="E31" t="s">
+        <v>99</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F58C16D2-AF12-4319-8F2F-54F224BCF579}">
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="8">
+        <f ca="1">TODAY()</f>
+        <v>46325</v>
+      </c>
+      <c r="F3" s="8">
+        <v>37466</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="9">
+        <f ca="1">NOW()</f>
+        <v>46325.518604398145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7">
+        <f ca="1">YEAR(C3)</f>
+        <v>2026</v>
+      </c>
+      <c r="F7">
+        <f>YEAR(F3)</f>
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8">
+        <f ca="1">MONTH(C3)</f>
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <f>MONTH(F3)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9">
+        <f ca="1">DAY(C3)</f>
+        <v>30</v>
+      </c>
+      <c r="F9">
+        <f>DAY(F3)</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10">
+        <f ca="1">WEEKDAY(TODAY(),2)</f>
+        <v>5</v>
+      </c>
+      <c r="F10">
+        <f ca="1">WEEKDAY(TODAY(),14)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11">
+        <f ca="1">WEEKNUM(TODAY())</f>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" t="str">
+        <f ca="1">TEXT(TODAY(),"MMMM")</f>
+        <v>October</v>
+      </c>
+      <c r="F12" t="str">
+        <f>TEXT(F3,"MMMM")</f>
+        <v>July</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C13" t="str">
+        <f ca="1">TEXT(TODAY(),"DDDD")</f>
+        <v>Friday</v>
+      </c>
+      <c r="F13" t="str">
+        <f>TEXT(F3,"DDDD")</f>
+        <v>Monday</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="8">
+        <v>45502</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C16" s="8">
+        <v>46324</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C17">
+        <f>DATEDIF(C15,C16,"Y")</f>
+        <v>2</v>
+      </c>
+      <c r="D17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C18">
+        <f>DATEDIF(C15,C16,"M")</f>
+        <v>27</v>
+      </c>
+      <c r="D18" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C19">
+        <f>DATEDIF(C15,C16,"D")</f>
+        <v>822</v>
+      </c>
+      <c r="D19" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" s="8">
+        <f ca="1">EDATE(TODAY(),3)</f>
+        <v>46417</v>
+      </c>
+      <c r="D21" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C23" s="8">
+        <f ca="1">EDATE(TODAY(),5)</f>
+        <v>46476</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC1B9222-F03B-4961-A111-C775684B0416}">
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="10">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="10">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="H3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="10">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F8" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" t="s">
+        <v>143</v>
+      </c>
+      <c r="F9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" t="s">
+        <v>144</v>
+      </c>
+      <c r="F10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" t="s">
+        <v>145</v>
+      </c>
+      <c r="F11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>146</v>
+      </c>
+      <c r="F12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>147</v>
+      </c>
+      <c r="F13" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
+        <v>149</v>
+      </c>
+      <c r="F15" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D16" t="s">
+        <v>150</v>
+      </c>
+      <c r="F16" t="s">
+        <v>154</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>151</v>
+      </c>
+      <c r="F17" t="s">
+        <v>155</v>
+      </c>
+      <c r="H17" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>152</v>
+      </c>
+      <c r="F18" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="19" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>153</v>
+      </c>
+      <c r="F19" t="s">
+        <v>157</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{5B6D9F51-9EB6-4AFF-B0B1-B898CE990501}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{1B93B88B-F55C-4E9F-AAB8-E544522171C8}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{4803913E-3C19-4256-A742-A36D30A283DB}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A35FB38-ED70-4CF8-A020-32BED4F01D66}">
+  <dimension ref="A1:K28"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I1" t="s">
+        <v>167</v>
+      </c>
+      <c r="K1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D2">
+        <f>AVERAGE(A2:A9)</f>
+        <v>44</v>
+      </c>
+      <c r="E2">
+        <f>SUM(A2:A9)</f>
+        <v>352</v>
+      </c>
+      <c r="F2">
+        <f>COUNT(A2:A9)</f>
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <f>E2/F2</f>
+        <v>44</v>
+      </c>
+      <c r="I2">
+        <f>A2-$D$2</f>
+        <v>-14</v>
+      </c>
+      <c r="K2">
+        <f>POWER(I2,2)</f>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>15</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I11" si="0">A3-$D$2</f>
+        <v>-29</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K10" si="1">POWER(I3,2)</f>
+        <v>841</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4">
+        <f>MEDIAN(A2:A9)</f>
+        <v>37.5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4">
+        <f>(8+1)/2</f>
+        <v>4.5</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>-19</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="1"/>
+        <v>361</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>30</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>-14</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="1"/>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D6">
+        <f>_xlfn.MODE.SNGL(A2:A9)</f>
+        <v>30</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>59</v>
+      </c>
+      <c r="C7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D7">
+        <f t="array" ref="D7:D10">_xlfn.MODE.MULT(A2:A10)</f>
+        <v>30</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="1"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>63</v>
+      </c>
+      <c r="D8">
+        <v>85</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="1"/>
+        <v>361</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>85</v>
+      </c>
+      <c r="D9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="1"/>
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>85</v>
+      </c>
+      <c r="D10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="1"/>
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>169</v>
+      </c>
+      <c r="D12">
+        <f>AVERAGE(K2:K10)</f>
+        <v>615.88888888888891</v>
+      </c>
+      <c r="E12" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>172</v>
+      </c>
+      <c r="C15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D15">
+        <f>SQRT(D12)</f>
+        <v>24.817108793912496</v>
+      </c>
+      <c r="E15">
+        <f>_xlfn.STDEV.P(A2:A10)</f>
+        <v>24.395405355704501</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>25</v>
+      </c>
+      <c r="D19">
+        <f>AVERAGE(A19:A25)</f>
+        <v>55.714285714285715</v>
+      </c>
+      <c r="E19">
+        <f>F19/G19</f>
+        <v>55.714285714285715</v>
+      </c>
+      <c r="F19">
+        <f>SUM(A19:A25)</f>
+        <v>390</v>
+      </c>
+      <c r="G19">
+        <f>COUNT(A19:A25)</f>
+        <v>7</v>
+      </c>
+      <c r="I19">
+        <f>A19-$D$19</f>
+        <v>-30.714285714285715</v>
+      </c>
+      <c r="J19">
+        <f>POWER(I19,2)</f>
+        <v>943.36734693877554</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>32</v>
+      </c>
+      <c r="I20">
+        <f t="shared" ref="I20:I25" si="2">A20-$D$19</f>
+        <v>-23.714285714285715</v>
+      </c>
+      <c r="J20">
+        <f t="shared" ref="J20:J24" si="3">POWER(I20,2)</f>
+        <v>562.36734693877554</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>46</v>
+      </c>
+      <c r="D21">
+        <f>MEDIAN(A19:A25)</f>
+        <v>46</v>
+      </c>
+      <c r="E21">
+        <f>(7+1)/2</f>
+        <v>4</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="2"/>
+        <v>-9.7142857142857153</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="3"/>
+        <v>94.367346938775526</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>46</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="2"/>
+        <v>-9.7142857142857153</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="3"/>
+        <v>94.367346938775526</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>64</v>
+      </c>
+      <c r="D23">
+        <f>_xlfn.MODE.SNGL(A19:A25)</f>
+        <v>46</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="2"/>
+        <v>8.2857142857142847</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="3"/>
+        <v>68.653061224489775</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>82</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="2"/>
+        <v>26.285714285714285</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="3"/>
+        <v>690.93877551020398</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>95</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="2"/>
+        <v>39.285714285714285</v>
+      </c>
+      <c r="J25">
+        <f>POWER(I25,2)</f>
+        <v>1543.3673469387754</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D27">
+        <f>AVERAGE(J19:J25)</f>
+        <v>571.0612244897959</v>
+      </c>
+      <c r="J27">
+        <f>SUM(J19:J25)</f>
+        <v>3997.4285714285711</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J28">
+        <f>J27/G19</f>
+        <v>571.0612244897959</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A20:A25">
+    <sortCondition ref="A20:A25"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{212E8D6B-4BC6-4D9C-93F1-76DA1FC52873}">
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="B2" s="10">
+        <v>9154</v>
+      </c>
+      <c r="C2" s="10">
+        <v>4069</v>
+      </c>
+      <c r="D2" s="10">
+        <v>1329</v>
+      </c>
+      <c r="E2" s="10">
+        <v>8685</v>
+      </c>
+      <c r="F2" s="10">
+        <v>6517</v>
+      </c>
+      <c r="G2" s="10">
+        <v>4359</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B3" s="10">
+        <v>8398</v>
+      </c>
+      <c r="C3" s="10">
+        <v>4343</v>
+      </c>
+      <c r="D3" s="10">
+        <v>6078</v>
+      </c>
+      <c r="E3" s="10">
+        <v>9610</v>
+      </c>
+      <c r="F3" s="10">
+        <v>8818</v>
+      </c>
+      <c r="G3" s="10">
+        <v>9199</v>
+      </c>
+      <c r="K3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="10">
+        <v>5230</v>
+      </c>
+      <c r="C4" s="10">
+        <v>9048</v>
+      </c>
+      <c r="D4" s="10">
+        <v>6600</v>
+      </c>
+      <c r="E4" s="10">
+        <v>6548</v>
+      </c>
+      <c r="F4" s="10">
+        <v>8228</v>
+      </c>
+      <c r="G4" s="10">
+        <v>2630</v>
+      </c>
+      <c r="K4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="B5" s="10">
+        <v>4376</v>
+      </c>
+      <c r="C5" s="10">
+        <v>1547</v>
+      </c>
+      <c r="D5" s="10">
+        <v>8529</v>
+      </c>
+      <c r="E5" s="10">
+        <v>7522</v>
+      </c>
+      <c r="F5" s="10">
+        <v>2959</v>
+      </c>
+      <c r="G5" s="10">
+        <v>7625</v>
+      </c>
+      <c r="K5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" s="10">
+        <v>6461</v>
+      </c>
+      <c r="C6" s="10">
+        <v>9768</v>
+      </c>
+      <c r="D6" s="10">
+        <v>3244</v>
+      </c>
+      <c r="E6" s="10">
+        <v>8452</v>
+      </c>
+      <c r="F6" s="10">
+        <v>9895</v>
+      </c>
+      <c r="G6" s="10">
+        <v>3711</v>
+      </c>
+      <c r="K6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="10">
+        <v>5163</v>
+      </c>
+      <c r="C7" s="10">
+        <v>3656</v>
+      </c>
+      <c r="D7" s="10">
+        <v>8129</v>
+      </c>
+      <c r="E7" s="10">
+        <v>1836</v>
+      </c>
+      <c r="F7" s="10">
+        <v>3508</v>
+      </c>
+      <c r="G7" s="10">
+        <v>8285</v>
+      </c>
+      <c r="K7" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B8" s="10">
+        <v>1398</v>
+      </c>
+      <c r="C8" s="10">
+        <v>3972</v>
+      </c>
+      <c r="D8" s="10">
+        <v>6061</v>
+      </c>
+      <c r="E8" s="10">
+        <v>4615</v>
+      </c>
+      <c r="F8" s="10">
+        <v>1496</v>
+      </c>
+      <c r="G8" s="10">
+        <v>8350</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:G8">
+    <cfRule type="cellIs" dxfId="17" priority="11" operator="greaterThan">
+      <formula>5000</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="10" operator="lessThan">
+      <formula>5000</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="9" operator="between">
+      <formula>8000</formula>
+      <formula>9000</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
+      <formula>4000</formula>
+    </cfRule>
+    <cfRule type="top10" dxfId="13" priority="4" rank="5"/>
+    <cfRule type="top10" dxfId="12" priority="3" percent="1" rank="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J10">
+    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
+      <formula>4625</formula>
+    </cfRule>
+    <cfRule type="top10" dxfId="10" priority="6" rank="4"/>
+    <cfRule type="top10" dxfId="9" priority="5" rank="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B8">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF555A"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{03A80FD0-7496-42E4-BA40-B948A0C04FEC}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C8">
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="4Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="25"/>
+        <cfvo type="percent" val="50"/>
+        <cfvo type="percent" val="75"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{03A80FD0-7496-42E4-BA40-B948A0C04FEC}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFF555A"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>B2:B8</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E923AF3C-E9E8-4A61-9B47-F5464826331F}">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1768,7 +4296,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E63F010-DED3-45D2-A132-931D2E30C71A}">
   <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2040,66 +4568,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C69E469F-FBB3-4F0E-A852-A8C4944018FB}">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1000</v>
-      </c>
-      <c r="B2">
-        <v>12</v>
-      </c>
-      <c r="F2">
-        <v>0.1</v>
-      </c>
-      <c r="G2">
-        <f>D2*F2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D3">
-        <f>A2*B2</f>
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C5">
-        <f>A2+100</f>
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <f>A2*0.1</f>
-        <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>